--- a/PS2/output/TABLE_1.xlsx
+++ b/PS2/output/TABLE_1.xlsx
@@ -380,13 +380,13 @@
         <v>4</v>
       </c>
       <c r="B2" t="n">
-        <v>6.16363637727273</v>
+        <v>5.95971701986685</v>
       </c>
       <c r="C2" t="n">
-        <v>4.614999995</v>
+        <v>4.25897388308274</v>
       </c>
       <c r="D2" t="n">
-        <v>1.54863638227273</v>
+        <v>1.70074313678411</v>
       </c>
     </row>
     <row r="3">
@@ -394,13 +394,13 @@
         <v>5</v>
       </c>
       <c r="B3" t="n">
-        <v>4.41428569047619</v>
+        <v>3.83914701144634</v>
       </c>
       <c r="C3" t="n">
-        <v>2.43157897421053</v>
+        <v>2.13338909257091</v>
       </c>
       <c r="D3" t="n">
-        <v>1.98270671626566</v>
+        <v>1.70575791887543</v>
       </c>
     </row>
     <row r="4">
@@ -408,13 +408,13 @@
         <v>6</v>
       </c>
       <c r="B4" t="n">
-        <v>1.74935068679654</v>
+        <v>2.12057000842051</v>
       </c>
       <c r="C4" t="n">
-        <v>2.18342102078947</v>
+        <v>2.12558479051184</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.434070333992937</v>
+        <v>-0.00501478209132511</v>
       </c>
     </row>
   </sheetData>
